--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>45406</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44952</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44952</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45012</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>46063</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>45152</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>44966</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>45810</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44648</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>45463</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45995</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>46031</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45187</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45033</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44955</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>44568</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44966</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45742</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>46031</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44489</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44650</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44475</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>44621</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44819</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44467</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44484</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>44480</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44480</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44713</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44855</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>44465</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44468</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44550</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44631</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44467</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44536</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44865</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44879</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44510</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44510</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44680</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44578</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44648</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44880</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44469</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44490</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44536</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44798</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45385</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44786</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44866</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>45356</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45145</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>45166</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44988</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45030</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44988</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>45448</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45211</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45104</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>45051</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45051</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>45012</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44964</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45635</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45635</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44910</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44910</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>45225</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>45749</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>45097</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>45772</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>45470</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>44953</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>44953</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44855</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45330</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45463</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45330</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>45051</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45448</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45749</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45434</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45546</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44824</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45166</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44770</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45054</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45054</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45300</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45152</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45152</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44903</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45239</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44868</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>45036</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>44904</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45012</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45012</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45223</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44693</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45236</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>45558</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>45753</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45212</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44489</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>45169</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45229</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>45070</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>45169</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45048</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>45671</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45357</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45275</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45096</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45188</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45152</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45152</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45194</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45551</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45093</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45247</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>44916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45097</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44895</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44994</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45434</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44819</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45169</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45190</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45247</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>44994</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45609</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45900</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44900</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45583</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45790</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45841</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>45460</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45629</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44972</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45804</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45015</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45635</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45901</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45697</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45904</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45477</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45477</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45195</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45763</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44930</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45910</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45678</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45411</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45266</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44469</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>45921</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45921</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45921</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45921</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45922</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45567</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44966</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>44979</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45237</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45371</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45371</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>45659</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45254</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45938</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45359</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45749</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45357</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45944</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45944</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>44551</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>45233</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45753</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44789</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>44616</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45951</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44638</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45952</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45583</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45187</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>44904</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45401</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45607</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45414</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45441</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>44866</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45975</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45975</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>45012</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45978</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>45852</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45040</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>45978</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>45978</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>45342</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45980</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45077</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45653</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45694</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44539</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>44539</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>46160</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>45642</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>46160</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44467</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>46160</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45463</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45048</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45749</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>45755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44988</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>44946</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45373</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>44928</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45999</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>45635</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45400</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>44960</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>46002</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>46005</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>46008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>46014</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45300</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45153</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45697</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45757</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>46029</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>46031</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>46033</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45274</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>44910</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45187</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45558</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45002</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44935</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44935</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45149</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45832</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44879</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44462</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>45051</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>46056</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>46056</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45636</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>46056</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>45763</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45763</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46055</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>46055</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>46055</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45749</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45561</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>46071</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>44726</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>46072</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45554</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>44678</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45469</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>46084</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45243</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>46084</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>46084</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>46084</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45532</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>46086</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>46086</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>46086</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45499</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44988</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>44965</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>44496</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45085</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44540</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>46189</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>46189</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45583</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45028</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45314</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>46104</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>46105</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45355</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45315</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45531</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45561</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44930</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45635</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45635</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>44953</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44903</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>46113</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>46202</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>46125</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45149</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>44641</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45635</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45701</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45265</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45280</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45370</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>44966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>44966</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45753</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>44550</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45390</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>44490</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45258</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45182</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45264</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44631</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45586</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45653</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45243</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44880</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>44900</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>46210</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45567</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45252</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>44523</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45751</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>44540</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45169</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44824</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>46212</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>46257</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45532</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45764</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>44999</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45558</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44525</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45749</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>45749</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44896</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>45213</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44960</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45636</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45676</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45048</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45749</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>46278</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45791</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>46282</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>46282</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45799</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>46282</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45798</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45653</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45810</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45810</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45817</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45817</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45825</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45832</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45832</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45412</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45607</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45845</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45763</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45856</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45672</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45609</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45062</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45411</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>45044</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45051</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44824</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44748</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45406</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>45406</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>44739</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45406</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45362</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45411</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45103</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44753</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45117</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45440</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45103</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44994</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45062</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45751</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45798</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45712</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45733</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45712</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46008</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>46031</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>46031</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46085</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46188</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>44607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45406</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>44952</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45343</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>46063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>44952</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45012</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45987</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>45152</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>44966</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>45810</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44490</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>45463</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>46031</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>45995</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45033</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44648</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45187</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45187</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44568</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44955</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44966</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45742</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>46031</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44489</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44650</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44475</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>44621</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44819</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44467</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44484</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>44480</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44480</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44713</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44855</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>44465</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44468</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44550</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>44631</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44550</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44467</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44536</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44865</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44879</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44680</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44510</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44510</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44578</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44648</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44880</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44469</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44490</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44536</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44798</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45434</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45371</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45371</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>45749</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>45252</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45300</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45441</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44910</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45463</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44539</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>46014</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44467</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>45015</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44966</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>44966</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44966</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45342</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>46029</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45275</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44540</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>44903</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>46031</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>46033</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45586</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44979</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45841</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>45609</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44895</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45635</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>45635</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45635</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44988</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45499</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>45901</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45804</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>44489</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45763</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>46055</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>46056</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>46056</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>46055</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>46056</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>46055</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45554</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45546</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45921</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45921</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45921</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45921</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45755</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45225</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45922</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>46071</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45561</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>46072</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45653</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>44935</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>44935</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>46084</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>46084</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>46084</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>46084</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>45810</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>45583</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>46086</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45051</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>46086</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>46086</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44953</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44953</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44964</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45653</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45938</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45944</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>44930</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45944</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44638</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45093</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45772</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45951</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>46104</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>46105</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44994</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44994</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45952</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45280</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45357</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>44965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>46113</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45567</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45028</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45629</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46125</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>44631</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>44960</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45975</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45978</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45978</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45975</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45817</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45166</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45978</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45583</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45978</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45980</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45697</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45749</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>45988</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>45904</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45635</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45701</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>44490</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45753</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45694</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45999</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45152</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45152</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>45817</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>46002</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>46005</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45223</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44855</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44988</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45030</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45237</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45166</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>45749</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>45900</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>46008</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44789</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44525</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>45985</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>44988</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44879</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45070</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45678</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45749</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>45266</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45825</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45077</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44910</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44916</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45213</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45832</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44999</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45832</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45401</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44868</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45096</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45012</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>44900</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44960</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45607</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>46160</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45412</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>46160</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45097</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>46160</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45040</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45448</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45845</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45330</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45330</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45051</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45182</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45561</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>45763</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>45856</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45832</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>44930</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>45532</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45152</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>45152</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>45162</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45470</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45477</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45477</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45672</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45012</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45247</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45085</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>44988</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45642</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45048</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45048</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45212</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>44616</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45274</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>46189</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>46189</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45469</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45036</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44551</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45636</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45551</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45169</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45149</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45635</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>46202</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>44550</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45190</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45097</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45558</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>46210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45051</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45188</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45659</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45676</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45697</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45653</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>46257</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>46212</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>44641</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45414</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45236</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45211</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45187</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44786</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>44824</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45187</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45753</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>45229</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45243</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45265</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45749</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45315</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>45314</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45355</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44496</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44819</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45300</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44540</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45258</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45264</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45195</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>46278</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45233</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45411</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45532</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>46282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>45583</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>46282</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>46282</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>46286</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45558</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44706</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>44900</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45400</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>46286</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44469</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>44770</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44693</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45390</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>44726</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46283</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>46283</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>46282</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45434</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44896</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45169</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45558</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44953</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45012</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45012</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>46289</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44972</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>44904</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>44910</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45531</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>44946</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45636</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44866</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45243</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45054</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>45054</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44824</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>45254</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45356</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45359</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45153</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>45753</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45145</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45048</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45607</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45149</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>44523</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45247</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>44866</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45385</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44880</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45169</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45763</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45763</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45051</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45460</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45104</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>44928</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45194</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45002</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45567</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>44678</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45373</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>45463</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45635</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45749</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45749</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45498</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45448</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>45751</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45357</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45635</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45370</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>45169</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>45671</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45764</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45749</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45791</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44739</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45609</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45062</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45411</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45044</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45051</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>44824</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44748</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45406</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45406</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45406</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45362</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45411</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45103</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>44753</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45117</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45440</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45103</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>44994</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45062</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45751</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45798</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45712</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45733</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45712</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46008</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46031</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46031</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>46085</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>46188</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>44607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45406</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>44952</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45343</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>46063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>44952</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45012</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45987</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>45152</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>44966</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>45810</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44490</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>45463</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>46031</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>45995</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45033</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44648</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45187</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45187</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44568</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44955</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44966</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45742</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>46031</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44489</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44650</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44475</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>44621</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44819</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44467</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44484</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>44480</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44480</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44713</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44855</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>44465</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44468</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44550</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>44631</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44550</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44467</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44536</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44865</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44879</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44680</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44510</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44510</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44578</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44648</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44880</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44469</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44490</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44536</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44798</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45434</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45371</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45371</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>45749</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>45252</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45300</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45441</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44910</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45463</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44539</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>46014</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44467</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>45015</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44966</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>44966</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44966</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45342</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>46029</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45275</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44540</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>44903</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>46031</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>46033</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45586</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44979</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45841</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>45609</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44895</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45635</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>45635</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45635</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44988</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45499</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>45901</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45804</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>44489</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45763</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>46055</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>46056</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>46056</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>46055</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>46056</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>46055</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45554</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45546</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45921</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45921</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45921</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45921</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45755</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45225</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45922</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>46071</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45561</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>46072</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45653</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>44935</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>44935</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>46084</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>46084</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>46084</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>46084</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>45810</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>45583</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>46086</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45051</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>46086</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>46086</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44953</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44953</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44964</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45653</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45938</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45944</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>44930</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45944</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44638</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45093</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45772</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45951</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>46104</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>46105</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44994</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44994</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45952</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45280</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45357</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>44965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>46113</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>45567</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45028</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45629</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46125</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>44631</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>44960</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45975</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45978</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45978</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45975</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45817</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45166</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45978</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45583</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45978</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45980</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45697</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45749</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>45988</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>45904</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45635</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45701</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>44490</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45753</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45694</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45999</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45152</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45152</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>45817</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>46002</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>46005</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45223</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44855</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44988</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45030</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45237</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45166</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>45749</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>45900</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>46008</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44789</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44525</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>45985</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>44988</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44879</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45070</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45678</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45749</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>45266</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45825</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45077</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44910</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44916</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45213</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45832</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44999</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45832</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45401</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44868</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45096</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45012</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>44900</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44960</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45607</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>46160</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45412</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>46160</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45097</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>46160</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45040</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45448</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45845</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45330</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45330</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45051</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45182</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45561</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>45763</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>45856</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45832</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>44930</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>45532</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45152</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>45152</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>45162</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45470</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45477</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45477</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45672</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45012</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45247</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45085</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>44988</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45642</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45048</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45048</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45212</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>44616</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45274</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>46189</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>46189</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45469</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45036</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44551</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45636</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45551</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45169</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45149</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45635</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>46202</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>44550</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45190</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45097</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45558</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>46210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45051</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45188</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45659</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45676</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45697</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45653</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>46257</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>46212</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>44641</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45414</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45236</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45211</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45187</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44786</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>44824</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45187</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45753</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>45229</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45243</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45265</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45749</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45315</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>45314</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45355</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44496</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44819</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45300</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44540</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45258</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45264</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45195</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>46278</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45233</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45411</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45532</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>46282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>45583</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>46282</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>46282</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>46286</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45558</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44706</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>44900</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45400</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>46286</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44469</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>44770</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44693</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45390</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>44726</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46283</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>46283</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>46282</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45434</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44896</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45169</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45558</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44953</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45012</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45012</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>46289</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44972</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>44904</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>44910</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45531</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>44946</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45636</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44866</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45243</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45054</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>45054</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44824</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>45254</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45356</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45359</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45153</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>45753</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45145</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45048</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45607</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45149</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>44523</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45247</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>44866</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45385</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44880</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45169</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45763</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45763</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45051</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45460</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45104</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>44928</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45194</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45002</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45567</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>44678</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45373</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>45463</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45635</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45749</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45749</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45498</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45448</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>45751</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45357</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45635</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45370</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>45169</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>45671</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45764</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45749</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45791</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44739</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45609</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45062</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45411</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45044</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45051</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>44824</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44748</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45406</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45406</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45406</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45362</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45411</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45103</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>44753</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45117</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45440</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45103</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>44994</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45062</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45751</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45798</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45712</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45733</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45712</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46008</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46031</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46031</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>46085</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>46188</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>45406</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44952</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44952</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>46063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45343</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45012</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>45152</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44648</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>46031</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45995</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45187</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45187</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44955</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>44568</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44966</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>46031</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44650</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44489</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44621</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44819</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44480</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44480</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44713</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44855</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44599</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44614</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44631</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44631</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44525</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44536</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44550</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>44865</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44879</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44680</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44510</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44578</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44648</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>44880</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44490</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44536</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>44798</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>44786</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45385</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45356</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44988</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44706</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45145</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45166</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>44988</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45448</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45030</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44964</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45211</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45051</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45635</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45051</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45012</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45772</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44953</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44953</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44910</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>44910</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>45097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45015</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45225</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45749</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45791</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>46005</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45470</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44855</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>46014</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45330</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45330</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45609</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45463</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>46029</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>46031</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45804</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45901</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>46033</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45448</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45763</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45546</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>45910</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>44770</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45166</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45152</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45152</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>45798</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45212</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45054</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45054</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45921</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45300</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>44903</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45921</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>45921</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>45921</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45922</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>46056</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>46056</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>46056</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>46055</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>46055</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>46055</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45239</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>44868</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45036</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45012</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45012</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>46071</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45223</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45938</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44693</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46072</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45653</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45944</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45810</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45944</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45558</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45753</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45229</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45236</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44489</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45810</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45070</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45951</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>46084</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45169</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45952</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>46084</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>46084</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>46084</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>46086</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46086</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>46086</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45357</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45048</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45671</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45817</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45817</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45096</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45275</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>45188</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45152</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45152</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45247</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45975</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>46104</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45194</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>46105</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>45978</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45978</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45978</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45978</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45980</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45551</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>46113</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45093</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45988</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44916</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45825</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>44895</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46125</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>44994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45434</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45999</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44819</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45832</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45169</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45190</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45832</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45247</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45701</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>44994</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45412</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>44900</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45607</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45583</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45753</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45460</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45629</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44972</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44490</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45635</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45697</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45845</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45477</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45477</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45195</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44930</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45411</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45985</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45900</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45790</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45498</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45856</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45567</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44966</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45904</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44979</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45237</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45371</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45371</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45659</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45254</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45678</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>45359</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45749</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45357</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44551</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45233</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45672</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45753</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>44789</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44616</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>44638</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45583</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45187</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>44904</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45401</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45607</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45414</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>45012</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45852</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45441</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>44866</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>46160</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>46160</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45040</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45342</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45077</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45653</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45694</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44539</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44539</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45642</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45832</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45463</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45841</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45749</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45755</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>44988</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44946</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45373</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44928</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45635</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45400</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44960</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>46189</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>46189</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45300</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45153</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>46202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45697</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>44550</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45274</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>46210</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>44910</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45187</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>46212</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45558</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45002</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44935</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>44935</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45149</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>46257</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>44879</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45051</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45636</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45763</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45763</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45749</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45561</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44726</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45554</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44678</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45469</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45243</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45532</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>46278</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45499</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>44988</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44965</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44496</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45085</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44540</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>46282</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>46282</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45583</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45028</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45314</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45355</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45315</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>46283</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>45531</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46282</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46286</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45561</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>44930</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45635</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45635</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46286</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46283</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44953</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>44903</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45149</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>44641</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45635</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>46289</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45265</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45280</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45370</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>44966</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>44966</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45390</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45258</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45182</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45264</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>44631</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45586</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45653</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45243</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>44880</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>46160</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44900</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45567</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45252</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44523</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45751</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44540</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45169</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>44824</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45532</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45764</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44999</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45558</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>44525</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45749</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45749</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>44896</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>45213</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>44960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45636</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45676</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>45048</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
         <v>45749</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>45609</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45062</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45411</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45044</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45051</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44824</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>44748</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45406</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45406</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>44739</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45406</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45362</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45411</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45103</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>44753</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45117</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45440</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45103</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44994</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45062</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45751</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45798</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45712</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45733</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45712</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46008</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>46031</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>46031</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>46085</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46188</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>45406</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44952</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44952</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>46063</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45343</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45012</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>45152</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44648</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>46031</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45995</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45187</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45187</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44955</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>44568</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44966</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>46031</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44650</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44489</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44621</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44588</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44819</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44480</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44480</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44713</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44855</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44599</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44614</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44631</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44631</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44525</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44536</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44550</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>44865</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44879</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44680</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44510</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44578</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44648</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>44880</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44490</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44536</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>44798</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>44786</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45385</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45356</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44988</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44706</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45145</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45166</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>44988</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45448</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45030</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44964</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45211</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45051</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45635</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45051</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45012</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45772</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44953</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44953</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44910</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>44910</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>45097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45015</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45225</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45749</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45791</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>46005</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45470</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44855</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>46014</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45330</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45330</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45609</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45463</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>46029</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>46031</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45804</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45901</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>46033</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45448</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45434</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45763</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45546</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>45910</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>44770</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45166</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45152</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45152</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>45798</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45212</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45054</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45054</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45921</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45300</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>44903</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45921</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>45921</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>45921</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45922</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>46056</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>46056</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>46056</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>46055</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>46055</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>46055</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45239</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>44868</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45036</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45012</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45012</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>46071</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45223</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45938</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44693</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46072</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45653</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45944</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45810</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45944</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45558</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45753</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45229</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45236</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44489</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45810</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45070</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45951</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>46084</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45169</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45952</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>46084</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>46084</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>46084</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>46086</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46086</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>46086</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45357</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45048</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45671</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45817</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45817</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45096</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45275</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>45188</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45152</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45152</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45247</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45975</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>46104</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45194</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>46105</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>45978</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45978</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45978</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45978</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45980</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45551</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>46113</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45093</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45988</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44916</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45825</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>44895</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46125</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>44994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45434</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45999</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44819</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45832</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45169</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45190</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45832</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45247</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45701</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>44994</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45412</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>44900</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45607</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45583</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45753</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45460</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45629</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44972</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44490</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45635</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45697</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45845</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45477</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45477</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45195</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44930</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45411</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45763</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45985</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45900</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45790</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45498</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45856</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45567</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44966</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45904</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44979</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45237</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45371</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45371</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45659</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45254</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45678</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>45359</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45749</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45357</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44551</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45233</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45672</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45753</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>44789</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44616</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>44638</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45583</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45187</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>44904</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45401</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45607</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45414</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>45012</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45852</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45441</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>44866</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>46160</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>46160</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45040</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45342</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45077</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45653</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45694</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44539</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>44539</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45642</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45832</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45463</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45841</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45749</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45755</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>44988</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44946</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45373</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44928</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45635</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45400</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44960</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>46189</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>46189</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45300</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45153</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>46202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45697</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>44550</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45274</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>46210</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>44910</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45187</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>46212</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45558</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45002</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44935</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>44935</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45149</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>46257</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>44879</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45051</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45636</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45763</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45763</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45749</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45561</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44726</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45554</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44678</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45469</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45243</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45532</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>46278</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45499</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>44988</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44965</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44496</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45085</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44540</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>46282</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>46282</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45583</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45028</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45314</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45355</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45315</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>46283</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>45531</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46282</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46286</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45561</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>44930</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45635</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45635</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46286</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46283</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44953</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>44903</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45149</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>44641</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45635</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>46289</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45265</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45280</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45370</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>44966</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>44966</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45390</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45258</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45182</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45264</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>44631</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45586</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45653</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45243</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>44880</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>46160</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44900</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45567</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45252</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44523</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45751</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44540</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45169</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>44824</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45532</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45764</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44999</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45558</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>44525</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45749</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45749</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>44896</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>45213</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>44960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45636</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45676</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>45048</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
         <v>45749</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>45609</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45062</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45411</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45044</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45051</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44824</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>44748</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45406</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45406</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>44739</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45406</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45362</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45411</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45103</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>44753</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45117</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45440</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45103</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44994</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45062</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45751</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45798</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45712</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45733</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45712</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46008</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>46031</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>46031</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>46085</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46188</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>44607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45406</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>44952</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45152</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>44952</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45012</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45987</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>46063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44490</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>45463</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44648</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45187</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45995</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>46031</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>45845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45033</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44568</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44955</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44966</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>46031</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44489</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44650</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44621</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44819</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44484</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>44480</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44713</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44855</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44599</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44865</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44525</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>44536</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>44680</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44510</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44816</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44578</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44490</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44550</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44648</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44536</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44631</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44631</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44798</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45153</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>44999</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45753</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45371</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45371</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45434</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45145</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45048</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45749</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>45607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45096</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>45252</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>45149</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44900</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44960</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44523</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45385</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44880</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>45097</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>45169</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>45300</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>45763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>45763</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>45441</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>44910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45051</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45040</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45460</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45104</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45448</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>45330</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>45330</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44928</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45051</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45463</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>44539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44539</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45182</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45561</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45194</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45567</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45015</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44678</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>45373</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45463</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45635</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>44966</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45342</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44930</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45841</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45749</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45749</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45532</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45275</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44540</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45152</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45152</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45498</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45470</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44903</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45448</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45901</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45751</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>45586</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45357</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45635</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>44979</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45370</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45169</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45804</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45671</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45635</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45764</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>45635</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45635</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45477</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45477</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44988</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45499</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45763</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45910</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45012</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45247</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45085</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44489</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45642</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45048</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45048</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45554</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45212</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44616</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45274</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45921</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45921</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>45921</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45921</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45546</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45922</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45755</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45225</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44904</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45791</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45469</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45561</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45653</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45036</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>44551</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44935</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44935</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45636</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45551</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45169</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45149</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45583</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45635</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45051</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44953</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44953</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44964</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45798</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>45190</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45097</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45558</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44638</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45093</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45051</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45810</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45772</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>45938</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45653</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45810</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44994</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>44994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45944</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45188</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45944</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>45659</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45676</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45280</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45697</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45357</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45817</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45817</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45567</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>45028</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45629</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45951</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45825</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44641</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>45414</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>44631</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44960</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45832</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45832</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45952</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45236</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45211</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45187</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45607</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45412</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45166</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45583</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>44786</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44824</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45697</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45187</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45753</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45749</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45845</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45229</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45243</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>45635</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45265</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45749</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45315</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45763</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45975</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45856</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45239</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45694</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45152</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45152</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45314</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45978</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45975</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45223</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45672</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>44855</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44988</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45030</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45355</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45166</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45749</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44496</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45978</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45980</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44819</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45300</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44789</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>44525</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>44540</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45258</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45264</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>44988</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45195</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>45233</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44879</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>45070</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45411</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45532</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45077</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>46104</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>46105</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44910</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45583</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44916</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45213</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45558</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>46113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>44706</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44900</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45400</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>46125</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44770</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45999</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44693</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45390</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>46002</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>44726</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>46005</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45434</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44896</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45169</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45904</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>45558</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>46008</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44953</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45701</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44490</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>46014</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45012</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45012</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>45753</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44972</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>44904</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>44910</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>46029</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45531</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>46031</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>44946</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>46033</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45636</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45790</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45900</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44866</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45243</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45054</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45054</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45985</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44824</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45678</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45254</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>45266</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>45356</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>45359</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>46055</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>46056</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>46055</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>46056</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>46055</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>45401</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>46071</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>46072</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45852</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45012</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>46084</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>46084</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46084</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>46084</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>46086</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46086</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>46086</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46160</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>46160</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45832</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46189</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>46189</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>46202</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>44550</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46210</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>46212</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>46278</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>46282</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>46282</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>46282</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>46286</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>46286</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>46283</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46283</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46282</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>46289</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>46160</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>46257</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>46303</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>46303</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>44739</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45609</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45062</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45411</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45044</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45051</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44824</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>44748</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45406</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45406</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>45406</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45362</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45411</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45103</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>44753</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45117</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45440</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45103</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>44994</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45751</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45798</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45712</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45733</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45712</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>46008</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>46031</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46031</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>46085</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>46188</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>44607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45406</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>44952</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45152</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>44952</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45012</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45987</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>46063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44490</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>45463</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44648</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45187</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45995</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>46031</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>45845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45033</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44568</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44955</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44966</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>46031</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44489</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44650</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44621</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44819</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44484</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>44480</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44713</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>44855</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44599</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44865</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44525</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>44536</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>44680</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44510</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44816</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44578</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44490</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44550</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44648</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44536</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44631</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44631</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>44550</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44798</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45153</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>44999</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45753</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45371</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45371</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45434</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45145</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45048</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45749</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>45607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45096</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>45252</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>45149</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44900</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44960</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44523</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45385</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44880</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>45097</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>45169</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>45300</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>45763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>45763</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>45441</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>44910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45051</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45040</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45460</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45104</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45448</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>45330</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>45330</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44928</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45051</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45463</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>44539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44539</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45182</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45561</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45194</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45567</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45015</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44678</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>45373</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45463</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45635</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>44966</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45342</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44930</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45841</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45749</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45749</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45532</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45275</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44540</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45152</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45152</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45498</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45470</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44903</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45448</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45901</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45751</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>45586</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45357</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45635</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>44979</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45370</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45169</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45804</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45671</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45635</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45764</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>45635</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45635</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45477</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45477</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44988</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45499</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45763</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45910</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45012</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45247</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45085</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44489</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45642</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45048</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45048</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45554</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45212</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44616</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45274</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45921</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45921</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>45921</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45921</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45546</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45922</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45755</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45225</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44904</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45791</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45469</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45561</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45653</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45036</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>44551</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44935</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44935</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45636</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45551</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45169</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45149</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45583</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45635</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45051</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44953</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44953</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>44964</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45798</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>45190</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45097</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45558</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44638</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45093</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45051</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45810</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45772</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>45938</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45653</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45810</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44994</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>44994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45944</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45188</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45944</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>45659</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45676</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45280</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45697</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45357</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45817</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45817</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45567</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>45028</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45629</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45951</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45825</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44641</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>45414</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>44631</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44960</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45832</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45832</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45952</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45236</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45211</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45187</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45607</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45412</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45166</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45583</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>44786</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44824</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45697</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45187</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45753</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45749</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45845</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45229</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45243</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>45635</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45265</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45749</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45315</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45763</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45975</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45856</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45239</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45694</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45152</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45152</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45314</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45978</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45975</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45223</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45672</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>44855</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44988</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45030</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45355</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45166</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45749</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44496</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45978</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45980</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44819</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45300</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44789</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>44525</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>44540</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45258</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45264</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>44988</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45195</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>45233</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44879</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>45070</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45411</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45532</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45077</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>46104</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>46105</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44910</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45583</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44916</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45213</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45558</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>46113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>44706</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44900</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45400</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>46125</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44770</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45999</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44693</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45390</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>46002</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>44726</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>46005</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45434</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44896</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45169</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45904</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>45558</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>46008</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44953</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45701</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44490</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>46014</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45012</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45012</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>45753</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44972</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>44904</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>44910</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>46029</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45531</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>46031</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>44946</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>46033</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45636</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45790</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45900</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44866</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45243</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45054</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45054</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45985</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44824</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45678</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45254</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>45266</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>45356</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>45359</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>46055</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>46056</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>46055</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>46056</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>46055</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>45401</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>46071</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>46072</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45852</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45012</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>46084</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>46084</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46084</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>46084</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>46086</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46086</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>46086</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46160</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>46160</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45832</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46189</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>46189</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>46202</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>44550</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46210</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>46212</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>46278</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>46282</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>46282</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>46282</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>46286</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>46286</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>46283</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46283</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46282</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>46289</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>46160</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>46257</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>46303</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>46303</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>44739</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45609</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45062</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45411</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45044</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45051</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44824</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>44748</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45406</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45406</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>45406</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45362</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45411</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45103</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>44753</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45117</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45440</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45103</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>44994</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45751</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45798</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45712</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45733</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45712</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>46008</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>46031</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46031</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>46085</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>46188</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45406</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44952</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>44952</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46063</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45012</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45152</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44648</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45463</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45995</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46031</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>45033</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44955</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44568</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44966</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>46031</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44489</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44650</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44621</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>44819</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44739</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>44713</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>44855</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>44599</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>44550</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>44631</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44631</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44536</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44816</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>44865</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44680</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44510</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44510</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>44578</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44648</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44880</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44490</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44536</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44798</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>45385</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44786</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44866</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44988</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>45145</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>45166</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>45030</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>44988</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45448</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45211</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>45104</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>45051</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>44964</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45051</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>45012</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>45772</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44910</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44910</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44953</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45635</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45097</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45225</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45749</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45470</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44855</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45330</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45330</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45463</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>45051</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>45749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>45448</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45434</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>45546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>44824</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44770</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>45166</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>45054</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45054</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45152</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45152</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45300</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45212</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45239</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44868</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45036</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>44904</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45012</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45012</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45223</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44693</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45558</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45753</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45169</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45229</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45236</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45070</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>44489</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45048</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45671</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45357</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45275</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>45096</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45188</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>45152</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>45152</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>45194</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45247</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>45097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45551</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45093</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>44916</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>45985</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>44895</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>45900</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>44994</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45790</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45609</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45434</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>44819</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>45841</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>45169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>45190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>45247</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45015</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45804</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45904</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45678</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45901</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45266</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>44900</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45583</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45460</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>45629</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44972</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45763</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45910</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45635</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45697</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45477</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45477</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45921</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45195</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45921</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45921</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>45921</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44930</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45411</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45922</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45498</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45938</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45401</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45567</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44966</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>45944</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44979</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45944</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>45237</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45371</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>45371</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45659</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45951</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>45952</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45012</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45254</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45852</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>45359</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45749</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45357</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44551</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>46160</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45233</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45753</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>46160</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>44789</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>44616</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45975</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>44638</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45975</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45978</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45583</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45978</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45187</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45980</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44904</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45607</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45414</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45441</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>44866</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45988</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45040</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45999</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45342</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>46002</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45077</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>46005</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45694</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>46008</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44539</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44539</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45642</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>46014</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45832</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45463</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45048</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45749</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45755</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44988</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>44946</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45373</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>46029</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>46031</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>44928</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45635</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45400</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46033</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44960</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>46056</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46056</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46055</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46055</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>46055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45300</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45153</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46071</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45697</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>46072</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>46084</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>46084</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>46084</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>46084</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45274</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>46086</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>46086</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>46086</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45162</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44910</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>46189</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>46189</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45187</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45558</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>45002</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>44935</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>44935</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45149</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>44879</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>46104</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>46105</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45051</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45636</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45763</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45763</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>46113</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45749</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45561</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>46125</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46202</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44726</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45554</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>44678</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45469</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45701</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45243</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45532</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44550</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45753</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45499</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>44988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44965</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>44490</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>44496</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45085</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>44540</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>46210</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45583</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45028</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45314</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>46212</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45355</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45315</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45531</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45561</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44930</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45635</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>45635</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>44953</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>44903</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45149</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>44641</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45635</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46278</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45265</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45280</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45370</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45390</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45258</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>45182</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>45264</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>44631</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45586</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45653</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>46282</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45243</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>46282</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44880</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44900</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>46283</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46282</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46286</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45567</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45252</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44523</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45751</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>46286</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>44540</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>46283</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45169</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44824</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45532</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45764</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>44999</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>46289</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45558</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44525</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45749</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45749</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>44896</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>45213</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44960</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>46160</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45636</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45676</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45048</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45749</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>46257</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>46303</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45791</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46303</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46265</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>44966</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>46265</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45798</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>46265</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>46265</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>46303</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46308</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45653</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45810</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>45810</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>45817</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45817</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45825</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45832</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>45832</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>45412</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45607</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45845</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45763</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45856</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45672</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45609</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45062</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45411</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45044</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45051</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>44824</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44748</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45406</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45406</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>44739</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45406</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45362</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45411</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45103</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44753</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45117</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45440</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45103</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44994</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45062</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>45751</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45798</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>45712</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45733</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45712</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>46008</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>46031</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>46031</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>46085</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>46188</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>1.6</v>
       </c>
       <c r="J2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -644,13 +644,13 @@
         <v>12</v>
       </c>
       <c r="S2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -695,6 +695,7 @@
 Spillkråka
 Stenfalk
 Tjäder
+Tofsmes
 Bred kärrtrollslända
 Buskskvätta
 Fiskgjuse
@@ -772,7 +773,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +902,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1028,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1149,7 @@
         <v>45406</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1258,7 +1259,7 @@
         <v>44952</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1377,7 +1378,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1496,7 +1497,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1610,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1724,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1836,7 +1837,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1943,7 +1944,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2055,7 +2056,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2168,7 @@
         <v>44952</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2273,7 +2274,7 @@
         <v>45343</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2379,7 +2380,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2486,7 @@
         <v>46063</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2596,7 +2597,7 @@
         <v>45012</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,7 +2703,7 @@
         <v>45152</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2809,7 @@
         <v>45104</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2920,7 @@
         <v>46295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3025,7 +3026,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3136,7 +3137,7 @@
         <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3247,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3351,7 +3352,7 @@
         <v>44648</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3456,7 +3457,7 @@
         <v>45463</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3561,7 +3562,7 @@
         <v>45995</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3666,7 +3667,7 @@
         <v>46031</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3776,7 +3777,7 @@
         <v>45187</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3886,7 +3887,7 @@
         <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3997,7 @@
         <v>45845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4101,7 +4102,7 @@
         <v>45033</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4210,7 +4211,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4315,7 +4316,7 @@
         <v>44955</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4426,7 @@
         <v>44568</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4531,7 @@
         <v>44966</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4640,7 +4641,7 @@
         <v>45742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4750,7 +4751,7 @@
         <v>46031</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4860,7 +4861,7 @@
         <v>44489</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4933,7 +4934,7 @@
         <v>44650</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5006,7 +5007,7 @@
         <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5079,7 +5080,7 @@
         <v>44621</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5152,7 +5153,7 @@
         <v>44588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5225,7 +5226,7 @@
         <v>44819</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5298,7 +5299,7 @@
         <v>44739</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5371,7 +5372,7 @@
         <v>44713</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5444,7 +5445,7 @@
         <v>44855</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5517,7 +5518,7 @@
         <v>44599</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5590,7 +5591,7 @@
         <v>44550</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5669,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5746,7 +5747,7 @@
         <v>44614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5819,7 +5820,7 @@
         <v>44631</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5897,7 +5898,7 @@
         <v>44631</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5970,7 +5971,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6048,7 +6049,7 @@
         <v>44536</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6121,7 +6122,7 @@
         <v>44816</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6194,7 +6195,7 @@
         <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6272,7 +6273,7 @@
         <v>44865</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6345,7 +6346,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6418,7 +6419,7 @@
         <v>44680</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6491,7 +6492,7 @@
         <v>44510</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6564,7 +6565,7 @@
         <v>44510</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6637,7 +6638,7 @@
         <v>44578</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6710,7 +6711,7 @@
         <v>44648</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6783,7 +6784,7 @@
         <v>44803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6856,7 +6857,7 @@
         <v>44880</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6929,7 +6930,7 @@
         <v>44490</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7007,7 +7008,7 @@
         <v>44536</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7085,7 +7086,7 @@
         <v>44798</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7158,7 +7159,7 @@
         <v>45385</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7231,7 +7232,7 @@
         <v>44786</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7304,7 +7305,7 @@
         <v>44866</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7377,7 +7378,7 @@
         <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7450,7 +7451,7 @@
         <v>44988</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7523,7 +7524,7 @@
         <v>44706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7596,7 +7597,7 @@
         <v>45145</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7669,7 +7670,7 @@
         <v>45166</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7742,7 +7743,7 @@
         <v>45030</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7815,7 +7816,7 @@
         <v>44988</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7888,7 +7889,7 @@
         <v>45448</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7966,7 +7967,7 @@
         <v>45211</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8044,7 +8045,7 @@
         <v>45104</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8122,7 +8123,7 @@
         <v>45051</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8195,7 +8196,7 @@
         <v>44964</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8268,7 +8269,7 @@
         <v>45051</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8341,7 +8342,7 @@
         <v>45012</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8414,7 +8415,7 @@
         <v>45772</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8487,7 +8488,7 @@
         <v>44910</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8565,7 +8566,7 @@
         <v>44910</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8643,7 +8644,7 @@
         <v>44953</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8721,7 +8722,7 @@
         <v>45635</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8799,7 +8800,7 @@
         <v>45635</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8877,7 +8878,7 @@
         <v>44953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8950,7 +8951,7 @@
         <v>45097</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9028,7 +9029,7 @@
         <v>45225</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9101,7 +9102,7 @@
         <v>45749</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9179,7 +9180,7 @@
         <v>45470</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9252,7 +9253,7 @@
         <v>44855</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9325,7 +9326,7 @@
         <v>45330</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9398,7 +9399,7 @@
         <v>45330</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9471,7 +9472,7 @@
         <v>45463</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9549,7 +9550,7 @@
         <v>45051</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9622,7 +9623,7 @@
         <v>45749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9700,7 +9701,7 @@
         <v>45448</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9773,7 +9774,7 @@
         <v>45434</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9851,7 +9852,7 @@
         <v>45546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9924,7 +9925,7 @@
         <v>44824</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9997,7 +9998,7 @@
         <v>44770</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10070,7 +10071,7 @@
         <v>45166</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10143,7 +10144,7 @@
         <v>45054</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10216,7 +10217,7 @@
         <v>45054</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10289,7 +10290,7 @@
         <v>45152</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10362,7 +10363,7 @@
         <v>45152</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10435,7 +10436,7 @@
         <v>45300</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10508,7 +10509,7 @@
         <v>45212</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10581,7 +10582,7 @@
         <v>44903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10654,7 +10655,7 @@
         <v>45239</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10727,7 +10728,7 @@
         <v>44868</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10800,7 +10801,7 @@
         <v>45036</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10873,7 +10874,7 @@
         <v>44904</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10946,7 +10947,7 @@
         <v>45012</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11019,7 +11020,7 @@
         <v>45012</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11092,7 +11093,7 @@
         <v>45223</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11165,7 +11166,7 @@
         <v>44693</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11243,7 +11244,7 @@
         <v>45558</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11321,7 +11322,7 @@
         <v>45753</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11399,7 +11400,7 @@
         <v>45169</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11472,7 +11473,7 @@
         <v>45229</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11545,7 +11546,7 @@
         <v>45236</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11618,7 +11619,7 @@
         <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11691,7 +11692,7 @@
         <v>45070</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11764,7 +11765,7 @@
         <v>44489</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11837,7 +11838,7 @@
         <v>45048</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11910,7 +11911,7 @@
         <v>45671</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11983,7 +11984,7 @@
         <v>45357</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12056,7 +12057,7 @@
         <v>45275</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12129,7 +12130,7 @@
         <v>45096</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12202,7 +12203,7 @@
         <v>45188</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12275,7 +12276,7 @@
         <v>45152</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12348,7 +12349,7 @@
         <v>45152</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12421,7 +12422,7 @@
         <v>45194</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12494,7 +12495,7 @@
         <v>45247</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12567,7 +12568,7 @@
         <v>45097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12640,7 +12641,7 @@
         <v>45551</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12718,7 +12719,7 @@
         <v>45093</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12791,7 +12792,7 @@
         <v>44916</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12869,7 +12870,7 @@
         <v>45985</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12942,7 +12943,7 @@
         <v>44895</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13015,7 +13016,7 @@
         <v>45900</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13088,7 +13089,7 @@
         <v>44994</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13166,7 +13167,7 @@
         <v>45790</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13239,7 +13240,7 @@
         <v>45609</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13317,7 +13318,7 @@
         <v>45434</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13395,7 +13396,7 @@
         <v>44819</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13468,7 +13469,7 @@
         <v>45841</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13541,7 +13542,7 @@
         <v>45169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13614,7 +13615,7 @@
         <v>45190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13687,7 +13688,7 @@
         <v>45247</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13760,7 +13761,7 @@
         <v>45015</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13833,7 +13834,7 @@
         <v>45804</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13911,7 +13912,7 @@
         <v>45904</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13984,7 +13985,7 @@
         <v>44994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14057,7 +14058,7 @@
         <v>45678</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14130,7 +14131,7 @@
         <v>45901</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14203,7 +14204,7 @@
         <v>45266</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14276,7 +14277,7 @@
         <v>44900</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14349,7 +14350,7 @@
         <v>45583</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14422,7 +14423,7 @@
         <v>45460</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14495,7 +14496,7 @@
         <v>45629</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14568,7 +14569,7 @@
         <v>44972</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14641,7 +14642,7 @@
         <v>45763</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14714,7 +14715,7 @@
         <v>45910</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14787,7 +14788,7 @@
         <v>45635</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14865,7 +14866,7 @@
         <v>45697</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14938,7 +14939,7 @@
         <v>45477</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15016,7 +15017,7 @@
         <v>45477</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15094,7 +15095,7 @@
         <v>45921</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15167,7 +15168,7 @@
         <v>45195</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15240,7 +15241,7 @@
         <v>45921</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15313,7 +15314,7 @@
         <v>45921</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15386,7 +15387,7 @@
         <v>45921</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15459,7 +15460,7 @@
         <v>44930</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15532,7 +15533,7 @@
         <v>45411</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15605,7 +15606,7 @@
         <v>45922</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15678,7 +15679,7 @@
         <v>45498</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15756,7 +15757,7 @@
         <v>45938</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15829,7 +15830,7 @@
         <v>45401</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15902,7 +15903,7 @@
         <v>45567</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15975,7 +15976,7 @@
         <v>44966</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16053,7 +16054,7 @@
         <v>45944</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16126,7 +16127,7 @@
         <v>44979</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16199,7 +16200,7 @@
         <v>45944</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16272,7 +16273,7 @@
         <v>45237</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16345,7 +16346,7 @@
         <v>45371</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16418,7 +16419,7 @@
         <v>45371</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16491,7 +16492,7 @@
         <v>45659</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16564,7 +16565,7 @@
         <v>45951</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16637,7 +16638,7 @@
         <v>45952</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16710,7 +16711,7 @@
         <v>45012</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16783,7 +16784,7 @@
         <v>45254</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16861,7 +16862,7 @@
         <v>45852</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16934,7 +16935,7 @@
         <v>45359</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17007,7 +17008,7 @@
         <v>45749</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17085,7 +17086,7 @@
         <v>45357</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17158,7 +17159,7 @@
         <v>44551</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17231,7 +17232,7 @@
         <v>46160</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17304,7 +17305,7 @@
         <v>45233</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17377,7 +17378,7 @@
         <v>45753</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17455,7 +17456,7 @@
         <v>46160</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17528,7 +17529,7 @@
         <v>44789</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17601,7 +17602,7 @@
         <v>44616</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17679,7 +17680,7 @@
         <v>45975</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17757,7 +17758,7 @@
         <v>44638</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17830,7 +17831,7 @@
         <v>45975</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17908,7 +17909,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17981,7 +17982,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18054,7 +18055,7 @@
         <v>45978</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18127,7 +18128,7 @@
         <v>45583</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18200,7 +18201,7 @@
         <v>45978</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18273,7 +18274,7 @@
         <v>45187</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18346,7 +18347,7 @@
         <v>45980</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18419,7 +18420,7 @@
         <v>44904</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18492,7 +18493,7 @@
         <v>45607</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18570,7 +18571,7 @@
         <v>45414</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18643,7 +18644,7 @@
         <v>45441</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18716,7 +18717,7 @@
         <v>44866</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18789,7 +18790,7 @@
         <v>45988</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18862,7 +18863,7 @@
         <v>45040</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18935,7 +18936,7 @@
         <v>45999</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19008,7 +19009,7 @@
         <v>45342</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19081,7 +19082,7 @@
         <v>46002</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19154,7 +19155,7 @@
         <v>45077</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19227,7 +19228,7 @@
         <v>46005</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19300,7 +19301,7 @@
         <v>45694</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19373,7 +19374,7 @@
         <v>46008</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19451,7 +19452,7 @@
         <v>44539</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19529,7 +19530,7 @@
         <v>44539</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19607,7 +19608,7 @@
         <v>45642</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19680,7 +19681,7 @@
         <v>46014</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19753,7 +19754,7 @@
         <v>45832</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19826,7 +19827,7 @@
         <v>45463</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19904,7 +19905,7 @@
         <v>45048</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19977,7 +19978,7 @@
         <v>45749</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20055,7 +20056,7 @@
         <v>45755</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20128,7 +20129,7 @@
         <v>44988</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20201,7 +20202,7 @@
         <v>44946</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20274,7 +20275,7 @@
         <v>45373</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20347,7 +20348,7 @@
         <v>46029</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20420,7 +20421,7 @@
         <v>46031</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20498,7 +20499,7 @@
         <v>44928</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20571,7 +20572,7 @@
         <v>45635</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20649,7 +20650,7 @@
         <v>45400</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20722,7 +20723,7 @@
         <v>46033</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20795,7 +20796,7 @@
         <v>44960</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20868,7 +20869,7 @@
         <v>46056</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20941,7 +20942,7 @@
         <v>46056</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21014,7 +21015,7 @@
         <v>46055</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21087,7 +21088,7 @@
         <v>46055</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21160,7 +21161,7 @@
         <v>46055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21233,7 +21234,7 @@
         <v>45300</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21306,7 +21307,7 @@
         <v>45153</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21379,7 +21380,7 @@
         <v>46071</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21452,7 +21453,7 @@
         <v>45697</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21525,7 +21526,7 @@
         <v>46072</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21598,7 +21599,7 @@
         <v>46084</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21671,7 +21672,7 @@
         <v>46084</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21744,7 +21745,7 @@
         <v>46084</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21817,7 +21818,7 @@
         <v>46084</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21890,7 +21891,7 @@
         <v>45274</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21963,7 +21964,7 @@
         <v>46086</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22036,7 +22037,7 @@
         <v>46086</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22109,7 +22110,7 @@
         <v>46086</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22182,7 +22183,7 @@
         <v>45162</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22255,7 +22256,7 @@
         <v>44910</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22333,7 +22334,7 @@
         <v>46189</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22406,7 +22407,7 @@
         <v>46189</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22479,7 +22480,7 @@
         <v>45187</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22552,7 +22553,7 @@
         <v>45558</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22630,7 +22631,7 @@
         <v>45002</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22703,7 +22704,7 @@
         <v>44935</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22776,7 +22777,7 @@
         <v>44935</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22849,7 +22850,7 @@
         <v>45149</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22922,7 +22923,7 @@
         <v>44879</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22995,7 +22996,7 @@
         <v>46104</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23068,7 +23069,7 @@
         <v>46105</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23141,7 +23142,7 @@
         <v>45051</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23214,7 +23215,7 @@
         <v>45636</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23292,7 +23293,7 @@
         <v>45763</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23370,7 +23371,7 @@
         <v>45763</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23448,7 +23449,7 @@
         <v>46113</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23521,7 +23522,7 @@
         <v>45749</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23599,7 +23600,7 @@
         <v>45561</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23672,7 +23673,7 @@
         <v>46125</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23745,7 +23746,7 @@
         <v>46202</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23818,7 +23819,7 @@
         <v>44726</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23891,7 +23892,7 @@
         <v>45554</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23969,7 +23970,7 @@
         <v>44678</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24042,7 +24043,7 @@
         <v>45469</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24115,7 +24116,7 @@
         <v>45701</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24188,7 +24189,7 @@
         <v>45243</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24261,7 +24262,7 @@
         <v>45532</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24334,7 +24335,7 @@
         <v>44550</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24407,7 +24408,7 @@
         <v>45753</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24485,7 +24486,7 @@
         <v>45499</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24563,7 +24564,7 @@
         <v>44988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24636,7 +24637,7 @@
         <v>44965</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24709,7 +24710,7 @@
         <v>44490</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24787,7 +24788,7 @@
         <v>44496</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24860,7 +24861,7 @@
         <v>45085</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24938,7 +24939,7 @@
         <v>44540</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25011,7 +25012,7 @@
         <v>46210</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25084,7 +25085,7 @@
         <v>45583</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25157,7 +25158,7 @@
         <v>45028</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25230,7 +25231,7 @@
         <v>45314</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25303,7 +25304,7 @@
         <v>46212</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25376,7 +25377,7 @@
         <v>45355</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25454,7 +25455,7 @@
         <v>45315</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25527,7 +25528,7 @@
         <v>45531</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25600,7 +25601,7 @@
         <v>45561</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25673,7 +25674,7 @@
         <v>44930</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25746,7 +25747,7 @@
         <v>45635</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25824,7 +25825,7 @@
         <v>45635</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25902,7 +25903,7 @@
         <v>44953</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25980,7 +25981,7 @@
         <v>44903</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26053,7 +26054,7 @@
         <v>45149</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26126,7 +26127,7 @@
         <v>44641</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26199,7 +26200,7 @@
         <v>45635</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26277,7 +26278,7 @@
         <v>46278</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26350,7 +26351,7 @@
         <v>45265</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26423,7 +26424,7 @@
         <v>45280</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26496,7 +26497,7 @@
         <v>45370</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26569,7 +26570,7 @@
         <v>45390</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26642,7 +26643,7 @@
         <v>45258</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26715,7 +26716,7 @@
         <v>45182</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26788,7 +26789,7 @@
         <v>45264</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26861,7 +26862,7 @@
         <v>44631</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26939,7 +26940,7 @@
         <v>45586</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27017,7 +27018,7 @@
         <v>45653</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27090,7 +27091,7 @@
         <v>46282</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27163,7 +27164,7 @@
         <v>45243</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27236,7 +27237,7 @@
         <v>46282</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27309,7 +27310,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27382,7 +27383,7 @@
         <v>44880</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27455,7 +27456,7 @@
         <v>44900</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27528,7 +27529,7 @@
         <v>46283</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27606,7 +27607,7 @@
         <v>46282</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27679,7 +27680,7 @@
         <v>46286</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27752,7 +27753,7 @@
         <v>45567</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27825,7 +27826,7 @@
         <v>45252</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27898,7 +27899,7 @@
         <v>44523</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27971,7 +27972,7 @@
         <v>45751</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28044,7 +28045,7 @@
         <v>46286</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28117,7 +28118,7 @@
         <v>44540</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28195,7 +28196,7 @@
         <v>46283</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28273,7 +28274,7 @@
         <v>45169</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28346,7 +28347,7 @@
         <v>44824</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28419,7 +28420,7 @@
         <v>45532</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28492,7 +28493,7 @@
         <v>45764</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28565,7 +28566,7 @@
         <v>44999</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28638,7 +28639,7 @@
         <v>46289</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28716,7 +28717,7 @@
         <v>45558</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28794,7 +28795,7 @@
         <v>44525</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28872,7 +28873,7 @@
         <v>45749</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28950,7 +28951,7 @@
         <v>45749</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29028,7 +29029,7 @@
         <v>44896</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29101,7 +29102,7 @@
         <v>45213</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29174,7 +29175,7 @@
         <v>44960</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29247,7 +29248,7 @@
         <v>46160</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29320,7 +29321,7 @@
         <v>45636</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29398,7 +29399,7 @@
         <v>45676</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29471,7 +29472,7 @@
         <v>45048</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29544,7 +29545,7 @@
         <v>45749</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29622,7 +29623,7 @@
         <v>46257</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29695,7 +29696,7 @@
         <v>46303</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29768,7 +29769,7 @@
         <v>45791</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29841,7 +29842,7 @@
         <v>46303</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29914,7 +29915,7 @@
         <v>46265</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29987,7 +29988,7 @@
         <v>44966</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30065,7 +30066,7 @@
         <v>46265</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30138,7 +30139,7 @@
         <v>45798</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30211,7 +30212,7 @@
         <v>46265</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30284,7 +30285,7 @@
         <v>46265</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30377,7 +30378,7 @@
         <v>46303</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30450,7 +30451,7 @@
         <v>46308</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30523,7 +30524,7 @@
         <v>45653</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30596,7 +30597,7 @@
         <v>45810</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30669,7 +30670,7 @@
         <v>45810</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30742,7 +30743,7 @@
         <v>45817</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30815,7 +30816,7 @@
         <v>45817</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30888,7 +30889,7 @@
         <v>45825</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30961,7 +30962,7 @@
         <v>45832</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31034,7 +31035,7 @@
         <v>45832</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31107,7 +31108,7 @@
         <v>45412</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31180,7 +31181,7 @@
         <v>45607</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31258,7 +31259,7 @@
         <v>45845</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31336,7 +31337,7 @@
         <v>45763</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31409,7 +31410,7 @@
         <v>45856</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31482,7 +31483,7 @@
         <v>45672</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31560,7 +31561,7 @@
         <v>45609</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31633,7 +31634,7 @@
         <v>45062</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31706,7 +31707,7 @@
         <v>45411</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31779,7 +31780,7 @@
         <v>45044</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31852,7 +31853,7 @@
         <v>45051</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31925,7 +31926,7 @@
         <v>44824</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31998,7 +31999,7 @@
         <v>44748</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32076,7 +32077,7 @@
         <v>45406</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32149,7 +32150,7 @@
         <v>45406</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32222,7 +32223,7 @@
         <v>44739</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32295,7 +32296,7 @@
         <v>45406</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32368,7 +32369,7 @@
         <v>45362</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32446,7 +32447,7 @@
         <v>45411</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32524,7 +32525,7 @@
         <v>45103</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32597,7 +32598,7 @@
         <v>44753</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32670,7 +32671,7 @@
         <v>45117</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32743,7 +32744,7 @@
         <v>45440</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32816,7 +32817,7 @@
         <v>45103</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32889,7 +32890,7 @@
         <v>44994</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32967,7 +32968,7 @@
         <v>45062</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33040,7 +33041,7 @@
         <v>45751</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33113,7 +33114,7 @@
         <v>45798</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33186,7 +33187,7 @@
         <v>45712</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33259,7 +33260,7 @@
         <v>45733</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33332,7 +33333,7 @@
         <v>45712</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33405,7 +33406,7 @@
         <v>46008</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33483,7 +33484,7 @@
         <v>46031</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33561,7 +33562,7 @@
         <v>46031</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33639,7 +33640,7 @@
         <v>46085</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33712,7 +33713,7 @@
         <v>46188</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>44607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45406</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44952</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45987</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>46063</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>46295</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45343</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44952</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45012</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45152</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45033</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45995</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46031</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44648</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45187</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>44568</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44955</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44966</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>45742</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>46031</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44650</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44588</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>44819</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44739</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44713</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44855</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>44599</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44550</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>44550</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>44631</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>44631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44525</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44816</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>44865</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44680</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>44510</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44510</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>44578</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44648</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44803</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44880</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44536</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>45434</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44896</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>45841</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>45609</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45169</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>45558</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45015</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>44953</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45901</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45804</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45012</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>45012</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>46160</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44904</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45763</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45910</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44910</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45531</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45636</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45921</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>45921</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45921</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45921</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45243</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45054</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45054</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45371</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45371</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45434</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45832</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44824</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45254</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45356</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45359</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45938</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45153</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45753</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>45944</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45749</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45252</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>45944</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45300</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45441</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45145</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45607</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>45149</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>45951</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44523</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45952</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45247</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44866</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45385</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44880</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45169</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45763</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45763</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45051</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45463</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45460</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>46189</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>46189</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45104</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44928</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45194</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44539</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44539</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>45002</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45567</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45975</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45978</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>45978</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45975</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44678</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45373</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45463</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>45978</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45980</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45635</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>46202</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45749</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45749</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>44550</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>45498</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>44903</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45448</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45751</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>46210</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45357</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45635</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45988</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45370</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45671</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>45764</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45749</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>46212</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45999</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>46002</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>46005</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>46278</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>46008</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>46014</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>46282</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>46029</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45791</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>46282</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>46282</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>46031</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>46286</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>46033</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>46286</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>46283</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>46283</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45798</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46282</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44966</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46055</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>46056</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>46055</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>46056</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46055</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45342</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45810</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>46289</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45653</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45810</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45817</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>46071</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>46072</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45275</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45825</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45832</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>46084</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>46084</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>46084</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>46084</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45832</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>46086</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>46086</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44540</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>46086</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45607</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45412</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>46160</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>44903</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>46257</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45845</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45586</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>46104</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>46105</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45763</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>44979</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45856</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>46113</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44895</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45672</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>46303</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>46125</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45635</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45635</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>46303</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44988</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>46265</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>46265</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45499</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>46265</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>46265</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>46308</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>44966</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45904</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45554</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45701</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45753</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45546</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>46314</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45755</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45225</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>46314</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44904</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45790</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>46314</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45561</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45900</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45653</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>46315</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45985</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44935</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>44935</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45678</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>46317</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>46318</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45583</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45051</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>44953</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>44964</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>46303</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44930</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45401</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44638</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45093</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45772</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45852</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44994</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44994</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>45012</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45280</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45357</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44965</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46160</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45567</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45028</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45629</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>44631</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44960</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45166</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45583</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>45697</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>45749</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45635</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45694</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45152</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45152</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>45223</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44855</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44988</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>45030</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45237</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45166</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>45749</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44789</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>44525</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44988</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44879</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45070</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45749</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45077</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44910</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>44916</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45213</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>44999</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>44868</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45096</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44900</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>44960</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45097</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45040</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45448</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45330</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45330</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45051</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45182</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45561</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>44930</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45532</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45152</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45152</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45162</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45470</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45477</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45477</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45012</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45247</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45085</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45642</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45048</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45048</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44616</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45274</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45469</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>45036</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44551</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45636</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45551</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45169</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45149</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45635</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45097</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45558</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45051</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45659</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45676</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45697</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>44641</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45414</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45236</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45211</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45187</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>44786</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44824</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45187</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45753</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45229</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45243</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>45265</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45749</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45315</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45239</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45314</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45355</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44496</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44819</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45300</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44540</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45258</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45264</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45195</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45233</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45411</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45532</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45583</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45558</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44706</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44900</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45400</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>44770</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44693</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45390</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44726</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44739</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45609</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45062</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45411</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45044</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45051</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>44824</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44748</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45406</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45406</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45406</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45362</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45411</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45103</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44753</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45117</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45440</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45103</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44994</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45062</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45751</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>45798</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45712</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>45733</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45712</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>46008</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>46031</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>46031</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>46085</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>46188</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>

--- a/Översikt VAGGERYD.xlsx
+++ b/Översikt VAGGERYD.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44955</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45369</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>44607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45406</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>44952</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>44818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>46127</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>43985</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45348</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45987</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>46063</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>46295</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45343</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44952</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45012</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45152</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>44966</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45033</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45995</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46031</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44648</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45187</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45187</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>44568</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44955</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44966</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>45742</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>46031</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44650</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44621</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44588</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>44819</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44739</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44713</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44855</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>44599</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44550</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>44550</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>44631</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>44631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44525</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44816</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>44865</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44680</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>44510</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44510</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>44578</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44648</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44803</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44880</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44536</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>45434</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44896</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>45841</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>45609</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45169</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>45558</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45015</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>44953</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45901</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45804</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45012</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>45012</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>46160</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44904</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45763</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45910</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44910</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45531</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45636</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45921</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>45921</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45921</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45921</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45243</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45054</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45054</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45371</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45371</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45434</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45832</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44824</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45254</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45356</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45359</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45938</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45153</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45753</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>45944</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45749</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45252</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>45944</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45300</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45441</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45145</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45607</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>45149</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>45951</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44523</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45952</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45247</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44866</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45385</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44880</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45169</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45763</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45763</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45051</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45463</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45460</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>46189</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>46189</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45104</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44928</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45194</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44539</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44539</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>45002</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45567</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45975</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45978</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>45978</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45975</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44678</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45373</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45463</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>45978</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45980</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45635</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>46202</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45749</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45749</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>44550</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>45498</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>44903</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45448</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45751</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>46210</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45357</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45635</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45988</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45370</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45671</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>45764</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45749</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>46212</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45999</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>46002</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>46005</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>46278</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>46008</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>46014</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>46282</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>46029</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45791</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>46282</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>46282</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>46031</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>46286</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>46033</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>46286</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>46283</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>46283</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45798</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46282</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44966</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46055</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>46056</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>46055</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>46056</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46055</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45342</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45810</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>46289</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45653</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45810</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45817</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>46071</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>46072</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45275</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45825</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45832</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>46084</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>46084</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>46084</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>46084</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45832</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>46086</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>46086</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44540</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>46086</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45607</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45412</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>46160</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>44903</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>46257</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45845</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45586</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>46104</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>46105</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45763</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>44979</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45856</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>46113</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44895</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45672</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>46303</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>46125</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45635</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45635</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>46303</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44988</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>46265</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>46265</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45499</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>46265</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>46265</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>46308</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>44966</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45904</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45554</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45701</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45753</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45546</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>46314</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45755</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45225</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>46314</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44904</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45790</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>46314</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45561</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45900</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45653</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>46315</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45985</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44935</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>44935</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45678</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>46317</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>46318</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45583</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45051</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>44953</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>44964</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>46303</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44930</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45401</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44638</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45093</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45772</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45852</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44994</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44994</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>45012</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45280</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45357</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44965</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46160</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45567</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45028</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45629</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>44631</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44960</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45166</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45583</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>45697</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>45749</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45635</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45694</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45152</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45152</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>45223</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44855</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44988</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>45030</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45237</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45166</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>45749</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44789</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>44525</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44988</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44879</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45070</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45749</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45077</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44910</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>44916</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45213</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>44999</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>44868</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45096</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44900</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>44960</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45097</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45040</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45448</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45330</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45330</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45051</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45182</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45561</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>44930</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45532</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45152</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45152</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45162</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45470</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45477</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45477</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45012</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45247</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45085</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45642</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45048</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45048</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44616</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45274</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45469</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>45036</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44551</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45636</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45551</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45169</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45149</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45635</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45097</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45558</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45051</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45659</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45676</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45697</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>44641</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45414</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45236</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45211</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45187</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>44786</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44824</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45187</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45753</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45229</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45243</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>45265</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45749</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45315</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45239</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45314</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45355</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44496</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44819</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45300</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44540</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45258</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45264</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45195</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45233</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45411</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45532</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45583</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45558</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44706</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44900</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45400</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>44770</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44693</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45390</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44726</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44739</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45609</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45062</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45411</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45044</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45051</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>44824</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44748</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45406</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45406</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45406</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45362</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45411</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45103</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44753</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45117</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45440</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45103</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44994</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45062</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45751</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>45798</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45712</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>45733</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45712</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>46008</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>46031</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>46031</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>46085</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>46188</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
